--- a/extenbooks/S708_extenbook.xlsx
+++ b/extenbooks/S708_extenbook.xlsx
@@ -17133,7 +17133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A150"/>
+  <dimension ref="A1:A201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17382,17 +17382,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>**S708** is the time-series exhibit Shaikh displays in Fig7.20. Period: 1962–1991.</t>
+          <t>**S708** is the exhibit Shaikh displays in Fig7.20 — the deviations of twenty Greek manufacturing</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>industries' incremental rates of profit (IROP, the return on newly added capital) from the overall</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Per the playbook recipe for `content_type = data_unavailable`:</t>
+          <t>average incremental rate, 1962–1991.</t>
         </is>
       </c>
     </row>
@@ -17402,27 +17406,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>&gt; "DPR + EPR documenting the chart-only source and why no underlying data exists ... L01 returns SKIPPED ... V03 returns PASS_DATA_UNAVAILABLE ... No chopped CSV."</t>
+          <t>Following the 2026-05-26 recovery (§0), this is a **digitized book-period series**, not a</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>`data_unavailable` one: the loader (`L01_S708`) reads the digitized panel workbook and emits the</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>## 2. Why it matters in Chapter 7</t>
+          <t>series, the validator (`V03_S708`) round-trips against it, and a chopped CSV is produced. (The</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>earlier `data_unavailable` handling — loader SKIPPED, validator `PASS_DATA_UNAVAILABLE`, no CSV — no</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ch7's empirical case for turbulent profit-rate equalization layers several exhibits: US BEA (S705–S710), the **Greek manufacturing pair (S707/S708)**, OECD STAN (S711), and the Christodoulopoulos (1995) world/US ISDB reconstruction (S703/S704). **S708 is the Greek manufacturing incremental-rate exhibit** — Shaikh's Fig 7.20, *"Deviations of Greek Manufacturing Incremental Profit Rates from Average Incremental Rate, 1962–1991"*, reproduced from Tsoulfidis &amp; Tsaliki (2011, p.30, fig. 5). *(Christodoulopoulos belongs to S703/S704 — a separate exhibit; an earlier draft of this paragraph mislabelled S708.)*</t>
+          <t>longer applies; it is retained below only as historical context.)</t>
         </is>
       </c>
     </row>
@@ -17432,7 +17444,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>## 2. Why it matters in Chapter 7</t>
         </is>
       </c>
     </row>
@@ -17442,21 +17454,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher | Status |</t>
+          <t>Ch7's empirical case for turbulent profit-rate equalization layers several exhibits: US BEA (S705–S710), the **Greek manufacturing pair (S707/S708)**, OECD STAN (S711), and the Christodoulopoulos (1995) world/US ISDB reconstruction (S703/S704). **S708 is the Greek manufacturing incremental-rate exhibit** — Shaikh's Fig 7.20, *"Deviations of Greek Manufacturing Incremental Profit Rates from Average Incremental Rate, 1962–1991"*, reproduced from Tsoulfidis &amp; Tsaliki (2011, p.30, fig. 5). *(Christodoulopoulos belongs to S703/S704 — a separate exhibit; an earlier draft of this paragraph mislabelled S708.)*</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>| S708-A (20 industries, digitized) | 1962–1991 | TSOULFIDIS_TSALIKI_2011_FIG5 | **book_period_validated** (provenance: digitized) |</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
@@ -17466,17 +17474,21 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Recovered by offline PDF vector extraction of MPRA 51334 Figure 6 (= the 2011 paper's Fig 5). The source is chart-only; the authors' exact tabulated panel is not redistributed. (The OECD-ISDB / Christodoulopoulos material belongs to the separate S703/S704 exhibit.)</t>
+          <t>| Subseries | Coverage | Publisher | Status |</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>|---|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>| S708-A (20 industries, digitized) | 1962–1991 | TSOULFIDIS_TSALIKI_2011_FIG5 | **book_period_validated** (provenance: digitized) |</t>
         </is>
       </c>
     </row>
@@ -17486,96 +17498,96 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Digitized industry panel (1962–1991, 20 two-digit Greek manufacturing industries):</t>
+          <t>Recovered by offline PDF vector extraction of MPRA 51334 Figure 6 (= the 2011 paper's Fig 5). The source is chart-only; the authors' exact tabulated panel is not redistributed. (The OECD-ISDB / Christodoulopoulos material belongs to the separate S703/S704 exhibit.)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>- `L01_S708` reads the digitized panel xlsx and emits long-form deviations via the shared</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  `_ch7_xlsx_panels.deviations_long` (subseries `S708-A-&lt;industry&gt;`).</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>- `P02_S708` canonicalises the schema via `_ch7_industry_panel_processor` → `data/processed/S708.parquet`.</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>- `V03_S708` round-trips against the panel's `*_Deviation` columns (`is_deviation=True`): PASS, n=600, MAE 0.0.</t>
+          <t>Digitized industry panel (1962–1991, 20 two-digit Greek manufacturing industries):</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>- Chopped: `chopped/S708.csv` (long: year, value, subseries_id, source_id, units, industry);</t>
+          <t>- `L01_S708` reads the digitized panel xlsx and emits long-form deviations via the shared</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Extenbook: `extenbooks/S708_extenbook.xlsx`.</t>
+          <t xml:space="preserve">  `_ch7_xlsx_panels.deviations_long` (subseries `S708-A-&lt;industry&gt;`).</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>- `P02_S708` canonicalises the schema via `_ch7_industry_panel_processor` → `data/processed/S708.parquet`.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>- `V03_S708` round-trips against the panel's `*_Deviation` columns (`is_deviation=True`): PASS, n=600, MAE 0.0.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>- Chopped: `chopped/S708.csv` (long: year, value, subseries_id, source_id, units, industry);</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Extenbook: `extenbooks/S708_extenbook.xlsx`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>- **Book period**: 1962–1991</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>- **Extension period**: not applicable (data_unavailable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rate deviation (decimal).</t>
+          <t>- **Extension period**: not applicable (no faithful time-extension of the Greek panel; see `S708_EPR.md` §2)</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17597,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -17595,21 +17607,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1. **No byte-exact reproduction possible** from local materials. The published figure stands as the authoritative record.</t>
+          <t>rate deviation (decimal).</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2. **PDF digitization** (WebPlotDigitizer) is technically possible but is a Phase 9 visualization task, not a Phase 5 data-ingestion task — and would introduce digitization noise that the No-Synthetic rule discourages for primary data.</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3. **No modern substitute** can splice onto the discontinued ISDB / unredistributed T&amp;T panel without violating the Anti-Degradation rule (industry-mapping drift, country-coverage drift, ESYE→ELSTAT methodology break). Any modern continuation is methodologically separate, not an extension.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
@@ -17619,31 +17627,31 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>1. **Digitization-grade, not table-exact.** The series was recovered by offline vector digitization of the source figure (§0), so it is faithful to the published chart rather than to the authors' exact underlying table (obtainable only by author request). Because the incremental-rate curves are high-frequency, per-year precision is lower than the average-rate panel (S707). The published figure remains the authoritative record.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2. **Digitization was performed as the book-period recovery**, using offline PDF vector extraction (no API calls), per-panel y-axis calibration, and clipping to 1962–1991. It is disclosed as `provenance: digitized`; it is a documented recovery of the authors' plotted points, not synthetic infill.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: `S039`</t>
+          <t>3. **No modern substitute** can splice onto the unredistributed Tsoulfidis &amp; Tsaliki Greek panel without violating the Anti-Degradation rule (industry-mapping drift and the 2010 ESYE→ELSTAT methodology break). Any modern continuation is methodologically separate, not an extension. *(The discontinued OECD-ISDB world/US splice concern belongs to the separate S703/S704 exhibit, not this Greek panel.)*</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 7 (Fig7.20); Appendix 7.1 II / IV (book pp. 856, 859).</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>- **B5 provenance document**: see SalvagedInputs/book_data/Reconstructed/ for the relevant `*_data_unavailable.md`.</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
@@ -17653,157 +17661,165 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>## 9. Validation</t>
+          <t>- **CD legacy ID**: `S039`</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>- **Book reference**: Shaikh (2016), Ch. 7 (Fig7.20); Appendix 7.1, sub-sections II / IV (book pp. 856, 859).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>- **V03 status**: `PASS` (is_deviation_panel; n_compared=600; MAE 0.0) — round-trip against the digitized panel.</t>
+          <t>- **Recovery documentation**: `Technical/WL1_Tsoulfidis_Tsaliki/EXTRACTION_REPORT.md` and the digitized workbook `SalvagedInputs/book_data/Reconstructed/Tsoulfidis_Tsaliki_2011_Fig5_S708.xlsx` (supersedes the earlier `*_data_unavailable.md` marker note, which predates the 2026-05-26 recovery).</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>- **Registry reference_values** (Decision 0002): subseries `S708-A-20-Food` at 1965/1975/1985 =</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.459 / -0.3014 / -0.3812 (tolerance 0.05, wider than S707 given the high-frequency series).</t>
+          <t>## 9. Validation</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Spot anchors from the digitized figure — provenance: digitized.</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>- **Fidelity note**: digitization-grade and lower-confidence than S707 (high-frequency IROP series);</t>
+          <t>- **V03 status**: `PASS` (is_deviation_panel; n_compared=600; MAE 0.0) — round-trip against the digitized panel.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>- **Registry reference_values** (Decision 0002): subseries `S708-A-20-Food` at 1965/1975/1985 =</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  0.459 / -0.3014 / -0.3812 (tolerance 0.05, wider than S707 given the high-frequency series).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Spot anchors from the digitized figure — provenance: digitized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>- **Fidelity note**: digitization-grade and lower-confidence than S707 (high-frequency IROP series);</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t xml:space="preserve">  not the authors' exact table.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="4">
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>- **IROP** — incremental rate of profit: the return on newly added capital (year-to-year change in profit over new investment), as distinct from the average rate of profit on the whole existing stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>- **Deviation** — an industry's rate minus the overall average rate that year; equalisation shows up as deviations crossing zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>- **Subseries (S708-A)** — a data line within series S708; here S708-A holds the 20-industry digitized panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>- **ESYE / ELSTAT** — the Greek national statistical service and its post-2010 successor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>- **ISDB** — OECD International Sectoral Database (relevant to the separate S703/S704 exhibit, not this Greek panel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>- **MPRA** — the Munich Personal RePEc Archive, which hosts the full-text source paper (working paper 51334).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset (legacy ID S039).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase 6** — Anu pipeline stages: ingestion / extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4">
         <f>== EPR: S708_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t># S708 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>**Series**: S708 — Figure 7.20 — Greek Manufacturing IROP Deviations, 1962–1991 (Tsoulfidis &amp; Tsaliki 2011 Fig 5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `data_unavailable`</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>**Extension method**: not applicable — see §1</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch7-fanout</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>**Related**: `S708_DPR.md`</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>## 1. Classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>`content_type = data_unavailable`. There is no byte-exact underlying dataset to extend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-    </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>## 2. Why no extension is attempted</t>
+          <t># S708 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -17813,41 +17829,49 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>- The original raw data (Christodoulopoulos 1995 / Tsoulfidis-Tsaliki 2011) is not redistributed in any public form; Shaikh did not redistribute it in his Appendix 7.2 either.</t>
+          <t>**Series**: S708 — Figure 7.20 — Greek Manufacturing Incremental-Profit-Rate Deviations, 1962–1991 (Tsoulfidis &amp; Tsaliki 2011 Fig 5)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>- The closest modern source (OECD STAN 2025 for the world / US tracks; ELSTAT post-2010 for the Greek track) has incompatible industry classifications, country coverage, capital-stock coverage, and (for Greece) a 2010 ESYE→ELSTAT methodology break.</t>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>- Any modern panel would be a methodologically separate exhibit, not a faithful extension. Per the Anti-Degradation rule, we do not splice.</t>
+          <t>**Construction classification**: `digitized` (book-period figure digitization — recovered 2026-05-26; supersedes the earlier `data_unavailable` classification)</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>**Extension method**: not applicable — no faithful time-extension exists (see §2)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>## 3. Method</t>
+          <t>**Authored**: 2026-05-18 · **Recovery update**: 2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>**Author**: opus-subagent-ch7-fanout</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>N/A.</t>
+          <t>**Related**: `S708_DPR.md`</t>
         </is>
       </c>
     </row>
@@ -17857,7 +17881,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -17867,7 +17891,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>**None attempted.** No proxy could meet the Anu No-Proxy bar.</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -17877,112 +17901,429 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>`provenance = digitized`, `status = book_period_validated`. This exhibit was **recovered by offline</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>figure digitization**: the plotted coordinates of Tsoulfidis &amp; Tsaliki (2011) Figure 5 — the</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>**None.** No interpolation, no digitization (digitization deferred to Phase 9 visualization, where it is appropriately constrained).</t>
+          <t>20-industry incremental-profit-rate (IROP) deviation grid Shaikh reproduces as Fig 7.20 (it appears</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>as Figure 6 in the 2013 MPRA revision, which inserted a new aggregate Fig 5) — were read directly</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>off the vector-drawn chart in MPRA working-paper 51334, per-panel calibrated to each panel's own</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>axis ticks, and clipped to Shaikh's 1962–1991 window. Method and validation are documented in the</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>| Failure | Action |</t>
+          <t>DPR (`S708_DPR.md` §0) and the extraction report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>(`Technical/WL1_Tsoulfidis_Tsaliki/EXTRACTION_REPORT.md`). There is a recovered book-period dataset;</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>| Loader invoked | Returns `{"status": "SKIPPED", "reason": "data_unavailable"}` — by design, not a failure |</t>
+          <t>there is no byte-exact underlying table to *extend* (that remains obtainable only from the authors).</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>| Validator invoked | Returns `{"status": "PASS_DATA_UNAVAILABLE"}` |</t>
-        </is>
-      </c>
+      <c r="A140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>**Confidence caveat.** The incremental-profit-rate (IROP) deviation series are intrinsically</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
+          <t>high-frequency, so per-year digitization fidelity is **lower than S707**. Treat S708 values as</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>approximate (`provenance: digitized`).</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>CD2 had no per-series CSV that matches this exhibit's content. The CD2-vs-RSCD comparison is not meaningful here.</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>## 2. Why no time-extension is attempted</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>## 8. Recovery paths (out-of-scope for Phase 6)</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>- The digitized panel reproduces the published figure faithfully but is not the authors' exact</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Documented in the B5 provenance file at `SalvagedInputs/book_data/Reconstructed/`. The two most plausible long-term recovery paths are:</t>
+          <t xml:space="preserve">  tabulated data, and Tsoulfidis &amp; Tsaliki did not redistribute the raw 1962–1991 series.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1. Author contact (T&amp;T are alive and contactable; Christodoulopoulos last known at NSSR).</t>
+          <t>- The closest modern source (ELSTAT — the Greek statistical service, successor to ESYE — for the</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2. PDF figure digitization via WebPlotDigitizer (Phase 9 visualization task; would be flagged `provenance: digitized`).</t>
+          <t xml:space="preserve">  post-2010 Greek track) has incompatible industry classifications, capital-stock coverage, and a</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2010 ESYE→ELSTAT methodology break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>- Any modern panel would be a methodologically separate exhibit, not a faithful continuation. Per</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the Anti-Degradation rule, we do not splice. *(The world/US OECD-ISDB continuation question belongs</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  to the separate S703/S704 Christodoulopoulos exhibit, not to this Greek panel.)*</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>## 3. Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>No time-extension. The book-period recovery method (offline PDF vector digitization of the source</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>figure) is described in `S708_DPR.md` §0/§4 and the extraction report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>## 4. No-Proxy disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>**None used.** No proxy series stands in for the Greek panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>The values are **digitized from the published chart** (`provenance: digitized`) — a documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>figure-digitization recovery of the authors' own plotted points, not fabricated, interpolated, or</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>frozen values. Because the incremental-rate curves are high-frequency, per-year precision is lower</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>than the average-rate panel (S707); the values are faithful to the figure's overall structure rather</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>than to an exact underlying table. No values were invented where the chart was unreadable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>## 6. Failure-mode table</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>| Failure | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>| Loader (`L01_S708`) invoked | Reads the digitized panel workbook and emits long-form deviations (no longer SKIPPED) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>| Validator (`V03_S708`) invoked | Round-trips against the panel's deviation columns: `PASS`, n=600, MAE 0.0 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>## 7. CD2 divergence pre-disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CD2 (the predecessor build) had no per-series CSV matching this exhibit's content. The CD2-vs-RSCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>comparison is not meaningful here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>## 8. Remaining recovery path (table-exact, out of scope for Phase 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>The book-period figure has already been recovered by digitization. The only outstanding path to the</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>authors' **exact** tabulated panel is **author contact** (Tsoulfidis &amp; Tsaliki are alive and</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>contactable). That would upgrade the provenance from `digitized` to a redistributed source table;</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>it is not required for the current book-period reproduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>- **IROP** — incremental rate of profit: the return on newly added capital (year-to-year change in profit over new investment), as distinct from the average rate of profit on the whole existing stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>- **Digitized (`provenance: digitized`)** — values recovered by reading coordinates off a published chart, faithful to the figure rather than to an exact underlying table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>- **ESYE / ELSTAT** — the Greek national statistical service and its post-2010 successor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>- **ISDB** — OECD International Sectoral Database (relevant to the separate S703/S704 exhibit, not this Greek panel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>- **MPRA** — the Munich Personal RePEc Archive (hosts the full-text source paper, working paper 51334).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase 6** — Anu pipeline stages: ingestion / extension.</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18839,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-26T19:02:16.102192+00:00</t>
+          <t>2026-07-02T06:25:22.175759+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S708_extenbook.xlsx
+++ b/extenbooks/S708_extenbook.xlsx
@@ -18839,7 +18839,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:25:22.175759+00:00</t>
+          <t>2026-07-11T03:44:26.107738+00:00</t>
         </is>
       </c>
     </row>
@@ -18854,11 +18854,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18881,6 +18881,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TSOULFIDIS_TSALIKI_2011_FIG5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Recovered (2026-05-26) by offline vector extraction of Tsoulfidis &amp; Tsaliki (2011) Fig 5 (= 2013 revision Fig 6) = Shaikh Fig 7.20 (MPRA 51334), clipped to 1962\u20131991; 20 Greek industries. provenance: digitized, lower per-year confidence than S707 because incremental-rate curves are high-frequency \u2014 values are approximate. Figure 7.20, title, period, and source verified against KB ch07; quotes verbatim-confirmed. Figure-overlay MATCH on structure (MINOR_DEV on per-point precision) per FIGURE_REPRO_ch07.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S708_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S708_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RSCD 2026-05-26: recovered via offline PDF vector extraction of the live MPRA 51334 copy (the 2011 Fig 5 = 2013 Fig 6 — vector-drawn 20-industry IROP-deviation panel), clipped to Shaikh's 1962-1991 window; flipped off data_unavailable (provenance: digitized). Lower per-year confidence than S707 (high-frequency series).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rate deviation (decimal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
